--- a/data/trans_orig/P19C10_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>605274</t>
+          <t>603834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649126</t>
+          <t>648992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1255371</t>
+          <t>1254692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1262480</t>
+          <t>1262489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12525</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1157564</t>
+          <t>1156606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929800</t>
+          <t>930681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939162</t>
+          <t>939366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2092183</t>
+          <t>2092825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2104818</t>
+          <t>2104593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674263</t>
+          <t>673587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>685072</t>
+          <t>685083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>912655</t>
+          <t>912834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>920753</t>
+          <t>920804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1591298</t>
+          <t>1590232</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1604287</t>
+          <t>1603910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883672</t>
+          <t>883443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1048084</t>
+          <t>1047789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1058793</t>
+          <t>1058780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1935875</t>
+          <t>1935082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947182</t>
+          <t>1947174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29381</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3335268</t>
+          <t>3334420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3350039</t>
+          <t>3349189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3549446</t>
+          <t>3549938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3565630</t>
+          <t>3565329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6890059</t>
+          <t>6891140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6912061</t>
+          <t>6911703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C10_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>686</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>609971</t>
+          <t>658230</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>603834</t>
+          <t>653107</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>650840</t>
+          <t>705463</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>648992</t>
+          <t>703818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1260812</t>
+          <t>1363693</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1254692</t>
+          <t>1358623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1262489</t>
+          <t>1365342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,98%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1164361</t>
+          <t>1013383</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1156606</t>
+          <t>1003334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>936143</t>
+          <t>1040180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>930681</t>
+          <t>1033521</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939366</t>
+          <t>1043786</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2100503</t>
+          <t>2053563</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2092825</t>
+          <t>2044228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2104593</t>
+          <t>2058406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>681244</t>
+          <t>768955</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>673587</t>
+          <t>761683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>685083</t>
+          <t>772790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>917460</t>
+          <t>789627</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>912834</t>
+          <t>784699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>920804</t>
+          <t>792740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1598704</t>
+          <t>1558582</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1590232</t>
+          <t>1549858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1603910</t>
+          <t>1563552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,22 +1824,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>888368</t>
+          <t>946355</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883443</t>
+          <t>942014</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1054523</t>
+          <t>1067193</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1047789</t>
+          <t>1059690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1058780</t>
+          <t>1071265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1942890</t>
+          <t>2013549</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1935082</t>
+          <t>2006063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947174</t>
+          <t>2018350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,22 +2097,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3343944</t>
+          <t>3386923</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3334420</t>
+          <t>3377137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3349189</t>
+          <t>3392659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3558965</t>
+          <t>3602464</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3549938</t>
+          <t>3592411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3565329</t>
+          <t>3609717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6902909</t>
+          <t>6989386</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6891140</t>
+          <t>6976499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6911703</t>
+          <t>6998740</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
